--- a/data/google_news_dedup_audit_23_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_23_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,397 +448,166 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7815289497375488</v>
+        <v>0.8914638757705688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Athleisure company Lululemon appoints Heidi O'Neill as new top boss, WSJ says - Reuters</t>
+          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lululemon says it picks former Nike executive Heidi O'Neill as next CEO - The Economic Times</t>
+          <t>UK Postcodes Update: Royal Mail Issued a Warning of Delivery Delays in 13 Postcodes | Check the full Postcodes list - The Sunday Guardian</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8443295955657959</v>
+        <v>0.8257030248641968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ottolenghi is Opening its First Ever Restaurant in Scotland - Time Out Worldwide</t>
+          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ottolenghi to open Scotland restaurant in Edinburgh - restaurantonline.co.uk</t>
+          <t>Royal Mail delivery delays hit 13 UK postcodes today — full list of affected areas - Daily Express</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7277969121932983</v>
+        <v>0.7208512425422668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon Launches GLP-1 Obesity Management Program via One Medical - thelec.net</t>
+          <t>The London Underground will be hit by four days of strikes this week - Time Out Worldwide</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon Announces Same-Day Delivery for GLP-1 Weight Loss Drugs - People.com</t>
+          <t>Full list of London Underground line delays and closures as second 24-hour strike hits - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7592941522598267</v>
+        <v>0.5720328688621521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon delivery station expected to bring dozens of jobs to Greenwood County, officials say - FOX Carolina</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Amazon plans to build delivery facility in Greenwood County, South Carolina - WYFF News 4</t>
+          <t>25 aprile. Fumarola sabato a manifestazione a Milano per 81° Liberazione - CISL - Confederazione Italiana Sindacati Lavoratori</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7863423228263855</v>
+        <v>0.7034305930137634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21-jarige man opgepakt voor dodelijke steekpartij in Stadspark Antwerpen - VRT</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nieuwe verdachte opgepakt voor dodelijke steekpartij in Stadspark - HLN</t>
+          <t>Atm Milano, sciopero il 24 aprile: stop a metro e mezzi nel venerdì della Design Week - Mentelocale</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8348290920257568</v>
+        <v>0.6787503957748413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21-jarige man opgepakt voor dodelijke steekpartij in Stadspark Antwerpen - VRT</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieuwe verdachte opgepakt voor dodelijke steekpartij in Antwerps Stadspark - Nieuwsblad</t>
+          <t>Weekend del 25-26 aprile a Milano: sagre, corteo, Fuorisalone e musei - inItaly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8630695343017578</v>
+        <v>0.6125665307044983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21-jarige man opgepakt voor dodelijke steekpartij in Stadspark Antwerpen - VRT</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nieuwe verdachte opgepakt voor dodelijke steekpartij in Antwerps Stadspark - MSN</t>
+          <t>Milano, Sala: sarà un 25 aprile delicato - Il Giorno</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>0.739797830581665</v>
+        <v>0.6682214736938477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21-jarige man opgepakt voor dodelijke steekpartij in Stadspark Antwerpen - VRT</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nieuwe verdachte opgepakt voor dodelijke steekpartij in Stadspark | Foto - pzc.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B10" t="n">
-        <v>27</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7300233244895935</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21-jarige man opgepakt voor dodelijke steekpartij in Stadspark Antwerpen - VRT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nieuwe verdachte opgepakt voor dodelijke steekpartij in Stadspark | Foto - HLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B11" t="n">
-        <v>26</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9766607880592346</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt ruim halfuur stil - HLN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Verdacht pakket ontdekt in wagon: treinverkeer op twee sporen in Brussel-Centraal ligt ruim halfuur stil | Foto - HLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" t="n">
-        <v>56</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.7174686193466187</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Polizei stoppt Autofahrer mit 1,5 Promille und ohne Führerschein - Augsburger Allgemeine</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ingolstadt: Frau kollidiert mit Hund und stürzt – Halter angezeigt - Augsburger Allgemeine</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>60</v>
-      </c>
-      <c r="B13" t="n">
-        <v>62</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7063714265823364</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Protesters stabbed at London rally against war on Iran - Al Jazeera</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Violence Erupts at London Protest Against Iran War - Oz Arab Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>63</v>
-      </c>
-      <c r="B14" t="n">
-        <v>66</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7048888802528381</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Barnet park double stabbing victims rushed to hospital as 'priority' - My London</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Two men taken to hospital after double stabbing on busy high street - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B15" t="n">
-        <v>71</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8271644115447998</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Second Tube strike to impact London from midday - BBC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>London faces more disruption as second 24-hour tube strike begins - The Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>70</v>
-      </c>
-      <c r="B16" t="n">
-        <v>79</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6535754203796387</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Second Tube strike to impact London from midday - BBC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>London Underground to Face Major Disruption with Tube Strike: Affected Lines and Travel Tips - Travel And Tour World</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>70</v>
-      </c>
-      <c r="B17" t="n">
-        <v>80</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.6748702526092529</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Second Tube strike to impact London from midday - BBC</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>When does the Tube strike end today? How long London Underground walkout lasts and why it's happening - The Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>81</v>
-      </c>
-      <c r="B18" t="n">
-        <v>82</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8290518522262573</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Venerdì 24 sciopero dei mezzi a Milano: a rischio metro, bus e tram - La Provincia Pavese</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>81</v>
-      </c>
-      <c r="B19" t="n">
-        <v>84</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8362529277801514</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Sciopero 24 aprile 2026, a Milano a rischio metro, bus e tram: orari, motivazioni, cosa sapere - Il Giorno</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>81</v>
-      </c>
-      <c r="B20" t="n">
-        <v>86</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7794240713119507</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Gli orari dello sciopero per metropolitana, bus e tram - Il Giorno</t>
+          <t>Design weekend del 25 e 26 aprile a Milano, cosa fare? Sagre, corteo, installazioni del Fuorisalone, musei gratis - Mentelocale</t>
         </is>
       </c>
     </row>
